--- a/outputs/120-24.xlsx
+++ b/outputs/120-24.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="44">
   <si>
     <t xml:space="preserve">FAH Parent Desc</t>
   </si>
@@ -328,48 +328,52 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -627,728 +631,585 @@
   <dimension ref="AY1:BN45"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="51" min="51" style="0" width="42.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="52" min="52" style="0" width="10.78"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="57" min="53" style="0" width="8.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="58" min="58" style="0" width="33.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="59" min="59" style="0" width="39.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="60" min="60" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="61" min="61" style="0" width="8.88"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="62" min="62" style="0" width="4.11"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="63" min="63" style="0" width="8.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="51" min="51" style="1" width="42.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="52" min="52" style="1" width="10.78"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="57" min="53" style="1" width="8.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="58" min="58" style="1" width="33.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="59" min="59" style="1" width="39.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="60" min="60" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="61" min="61" style="1" width="8.88"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="62" min="62" style="1" width="4.11"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="63" min="63" style="1" width="8.88"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="AY1" s="1" t="s">
+      <c r="AY1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="BF1" s="2" t="s">
+      <c r="BF1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="BG1" s="3" t="s">
+      <c r="BG1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="BL1" s="1" t="s">
+      <c r="BL1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AY2" s="4" t="s">
+      <c r="AY2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="BF2" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="BG2" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="BL2" s="0" t="s">
+      <c r="BF2" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="BG2" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="BL2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="BN2" s="0" t="str">
-        <f aca="false">IF(AND(BL2="LAG",OR(BG2="OCOGS - Spares - Transfer Price Overhead",BG2="OFSS - ORCL Consulting Prod Cost I/C")),IF(OR(AY2="BOA_033E",AY2="BOA_011G"),"OCOGS - Spares - Transfer Price Overhead","OFSS - ORCL Consulting Prod Cost I/C"),"")</f>
-        <v/>
-      </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AY3" s="4" t="s">
+      <c r="AY3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="BF3" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="BG3" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="BL3" s="0" t="s">
+      <c r="BF3" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="BG3" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="BL3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="BN3" s="0" t="str">
-        <f aca="false">IF(AND(BL3="LAG",OR(BG3="OCOGS - Spares - Transfer Price Overhead",BG3="OFSS - ORCL Consulting Prod Cost I/C")),IF(OR(AY3="BOA_033E",AY3="BOA_011G"),"OCOGS - Spares - Transfer Price Overhead","OFSS - ORCL Consulting Prod Cost I/C"),"")</f>
-        <v/>
-      </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AY4" s="4" t="s">
+      <c r="AY4" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="BG4" s="6" t="s">
+      <c r="BG4" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="BL4" s="0" t="s">
+      <c r="BL4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="BN4" s="0" t="str">
-        <f aca="false">IF(AND(BL4="LAG",OR(BG4="OCOGS - Spares - Transfer Price Overhead",BG4="OFSS - ORCL Consulting Prod Cost I/C")),IF(OR(AY4="BOA_033E",AY4="BOA_011G"),"OCOGS - Spares - Transfer Price Overhead","OFSS - ORCL Consulting Prod Cost I/C"),"")</f>
-        <v/>
-      </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AY5" s="4" t="s">
+      <c r="AY5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="BG5" s="6" t="s">
+      <c r="BG5" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="BL5" s="0" t="s">
+      <c r="BL5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="BN5" s="0" t="str">
-        <f aca="false">IF(AND(BL5="LAG",OR(BG5="OCOGS - Spares - Transfer Price Overhead",BG5="OFSS - ORCL Consulting Prod Cost I/C")),IF(OR(AY5="BOA_033E",AY5="BOA_011G"),"OCOGS - Spares - Transfer Price Overhead","OFSS - ORCL Consulting Prod Cost I/C"),"")</f>
-        <v/>
-      </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AY6" s="4" t="s">
+      <c r="AY6" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="BF6" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="BG6" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="BL6" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="BN6" s="0" t="str">
-        <f aca="false">IF(AND(BL6="LAG",OR(BG6="OCOGS - Spares - Transfer Price Overhead",BG6="OFSS - ORCL Consulting Prod Cost I/C")),IF(OR(AY6="BOA_033E",AY6="BOA_011G"),"OCOGS - Spares - Transfer Price Overhead","OFSS - ORCL Consulting Prod Cost I/C"),"")</f>
-        <v>OCOGS - Spares - Transfer Price Overhead</v>
+      <c r="BF6" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="BG6" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="BL6" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="BN6" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AY7" s="4" t="s">
+      <c r="AY7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="BF7" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="BG7" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="BL7" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="BN7" s="0" t="str">
-        <f aca="false">IF(AND(BL7="LAG",OR(BG7="OCOGS - Spares - Transfer Price Overhead",BG7="OFSS - ORCL Consulting Prod Cost I/C")),IF(OR(AY7="BOA_033E",AY7="BOA_011G"),"OCOGS - Spares - Transfer Price Overhead","OFSS - ORCL Consulting Prod Cost I/C"),"")</f>
-        <v>OCOGS - Spares - Transfer Price Overhead</v>
+      <c r="BF7" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="BG7" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="BL7" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="BN7" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AY8" s="8" t="s">
+      <c r="AY8" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="BG8" s="6" t="s">
+      <c r="BG8" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="BL8" s="0" t="s">
+      <c r="BL8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="BN8" s="0" t="str">
-        <f aca="false">IF(AND(BL8="LAG",OR(BG8="OCOGS - Spares - Transfer Price Overhead",BG8="OFSS - ORCL Consulting Prod Cost I/C")),IF(OR(AY8="BOA_033E",AY8="BOA_011G"),"OCOGS - Spares - Transfer Price Overhead","OFSS - ORCL Consulting Prod Cost I/C"),"")</f>
-        <v/>
-      </c>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AY9" s="8" t="s">
+      <c r="AY9" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="BF9" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="BG9" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="BL9" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="BN9" s="0" t="str">
-        <f aca="false">IF(AND(BL9="LAG",OR(BG9="OCOGS - Spares - Transfer Price Overhead",BG9="OFSS - ORCL Consulting Prod Cost I/C")),IF(OR(AY9="BOA_033E",AY9="BOA_011G"),"OCOGS - Spares - Transfer Price Overhead","OFSS - ORCL Consulting Prod Cost I/C"),"")</f>
-        <v>OFSS - ORCL Consulting Prod Cost I/C</v>
+      <c r="BF9" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="BG9" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="BL9" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="BN9" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AY10" s="8" t="s">
+      <c r="AY10" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="BF10" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="BG10" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="BL10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="BN10" s="0" t="str">
-        <f aca="false">IF(AND(BL10="LAG",OR(BG10="OCOGS - Spares - Transfer Price Overhead",BG10="OFSS - ORCL Consulting Prod Cost I/C")),IF(OR(AY10="BOA_033E",AY10="BOA_011G"),"OCOGS - Spares - Transfer Price Overhead","OFSS - ORCL Consulting Prod Cost I/C"),"")</f>
-        <v>OFSS - ORCL Consulting Prod Cost I/C</v>
+      <c r="BF10" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="BG10" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="BL10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="BN10" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AY11" s="8" t="s">
+      <c r="AY11" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="BG11" s="8" t="s">
+      <c r="BG11" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="BL11" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="BN11" s="0" t="str">
-        <f aca="false">IF(AND(BL11="LAG",OR(BG11="OCOGS - Spares - Transfer Price Overhead",BG11="OFSS - ORCL Consulting Prod Cost I/C")),IF(OR(AY11="BOA_033E",AY11="BOA_011G"),"OCOGS - Spares - Transfer Price Overhead","OFSS - ORCL Consulting Prod Cost I/C"),"")</f>
-        <v/>
+      <c r="BL11" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AY12" s="8" t="s">
+      <c r="AY12" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="BG12" s="8" t="s">
+      <c r="BG12" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="BL12" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="BN12" s="0" t="str">
-        <f aca="false">IF(AND(BL12="LAG",OR(BG12="OCOGS - Spares - Transfer Price Overhead",BG12="OFSS - ORCL Consulting Prod Cost I/C")),IF(OR(AY12="BOA_033E",AY12="BOA_011G"),"OCOGS - Spares - Transfer Price Overhead","OFSS - ORCL Consulting Prod Cost I/C"),"")</f>
-        <v/>
+      <c r="BL12" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AY13" s="4" t="s">
+      <c r="AY13" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="BF13" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="BG13" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="BL13" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="BN13" s="0" t="str">
-        <f aca="false">IF(AND(BL13="LAG",OR(BG13="OCOGS - Spares - Transfer Price Overhead",BG13="OFSS - ORCL Consulting Prod Cost I/C")),IF(OR(AY13="BOA_033E",AY13="BOA_011G"),"OCOGS - Spares - Transfer Price Overhead","OFSS - ORCL Consulting Prod Cost I/C"),"")</f>
-        <v>OCOGS - Spares - Transfer Price Overhead</v>
+      <c r="BF13" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="BG13" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="BL13" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="BN13" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AY14" s="4" t="s">
+      <c r="AY14" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="BF14" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="BG14" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="BL14" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="BN14" s="0" t="str">
-        <f aca="false">IF(AND(BL14="LAG",OR(BG14="OCOGS - Spares - Transfer Price Overhead",BG14="OFSS - ORCL Consulting Prod Cost I/C")),IF(OR(AY14="BOA_033E",AY14="BOA_011G"),"OCOGS - Spares - Transfer Price Overhead","OFSS - ORCL Consulting Prod Cost I/C"),"")</f>
-        <v>OCOGS - Spares - Transfer Price Overhead</v>
+      <c r="BF14" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="BG14" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="BL14" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="BN14" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AY15" s="8" t="s">
+      <c r="AY15" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="BG15" s="8" t="s">
+      <c r="BG15" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="BL15" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="BN15" s="0" t="str">
-        <f aca="false">IF(AND(BL15="LAG",OR(BG15="OCOGS - Spares - Transfer Price Overhead",BG15="OFSS - ORCL Consulting Prod Cost I/C")),IF(OR(AY15="BOA_033E",AY15="BOA_011G"),"OCOGS - Spares - Transfer Price Overhead","OFSS - ORCL Consulting Prod Cost I/C"),"")</f>
-        <v/>
+      <c r="BL15" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AY16" s="8" t="s">
+      <c r="AY16" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="BF16" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="BG16" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="BL16" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="BN16" s="0" t="str">
-        <f aca="false">IF(AND(BL16="LAG",OR(BG16="OCOGS - Spares - Transfer Price Overhead",BG16="OFSS - ORCL Consulting Prod Cost I/C")),IF(OR(AY16="BOA_033E",AY16="BOA_011G"),"OCOGS - Spares - Transfer Price Overhead","OFSS - ORCL Consulting Prod Cost I/C"),"")</f>
-        <v>OFSS - ORCL Consulting Prod Cost I/C</v>
+      <c r="BF16" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="BG16" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="BL16" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="BN16" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AY17" s="8" t="s">
+      <c r="AY17" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="BF17" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="BG17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="BL17" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="BN17" s="0" t="str">
-        <f aca="false">IF(AND(BL17="LAG",OR(BG17="OCOGS - Spares - Transfer Price Overhead",BG17="OFSS - ORCL Consulting Prod Cost I/C")),IF(OR(AY17="BOA_033E",AY17="BOA_011G"),"OCOGS - Spares - Transfer Price Overhead","OFSS - ORCL Consulting Prod Cost I/C"),"")</f>
-        <v>OFSS - ORCL Consulting Prod Cost I/C</v>
+      <c r="BF17" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="BG17" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="BL17" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="BN17" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AY18" s="8" t="s">
+      <c r="AY18" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="BG18" s="8" t="s">
+      <c r="BG18" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="BL18" s="0" t="s">
+      <c r="BL18" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="BN18" s="0" t="str">
-        <f aca="false">IF(AND(BL18="LAG",OR(BG18="OCOGS - Spares - Transfer Price Overhead",BG18="OFSS - ORCL Consulting Prod Cost I/C")),IF(OR(AY18="BOA_033E",AY18="BOA_011G"),"OCOGS - Spares - Transfer Price Overhead","OFSS - ORCL Consulting Prod Cost I/C"),"")</f>
-        <v/>
-      </c>
     </row>
     <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AY19" s="8" t="s">
+      <c r="AY19" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="BG19" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="BL19" s="0" t="s">
+      <c r="BG19" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="BL19" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="BN19" s="0" t="str">
-        <f aca="false">IF(AND(BL19="LAG",OR(BG19="OCOGS - Spares - Transfer Price Overhead",BG19="OFSS - ORCL Consulting Prod Cost I/C")),IF(OR(AY19="BOA_033E",AY19="BOA_011G"),"OCOGS - Spares - Transfer Price Overhead","OFSS - ORCL Consulting Prod Cost I/C"),"")</f>
-        <v/>
-      </c>
     </row>
     <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AY20" s="8" t="s">
+      <c r="AY20" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="BG20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="BL20" s="0" t="s">
+      <c r="BG20" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="BL20" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="BN20" s="0" t="str">
-        <f aca="false">IF(AND(BL20="LAG",OR(BG20="OCOGS - Spares - Transfer Price Overhead",BG20="OFSS - ORCL Consulting Prod Cost I/C")),IF(OR(AY20="BOA_033E",AY20="BOA_011G"),"OCOGS - Spares - Transfer Price Overhead","OFSS - ORCL Consulting Prod Cost I/C"),"")</f>
-        <v/>
-      </c>
     </row>
     <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AY21" s="4" t="s">
+      <c r="AY21" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="BG21" s="8" t="s">
+      <c r="BG21" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="BL21" s="0" t="s">
+      <c r="BL21" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="BN21" s="0" t="str">
-        <f aca="false">IF(AND(BL21="LAG",OR(BG21="OCOGS - Spares - Transfer Price Overhead",BG21="OFSS - ORCL Consulting Prod Cost I/C")),IF(OR(AY21="BOA_033E",AY21="BOA_011G"),"OCOGS - Spares - Transfer Price Overhead","OFSS - ORCL Consulting Prod Cost I/C"),"")</f>
-        <v/>
-      </c>
     </row>
     <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AY22" s="4" t="s">
+      <c r="AY22" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="BG22" s="8" t="s">
+      <c r="BG22" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="BL22" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="BN22" s="0" t="str">
-        <f aca="false">IF(AND(BL22="LAG",OR(BG22="OCOGS - Spares - Transfer Price Overhead",BG22="OFSS - ORCL Consulting Prod Cost I/C")),IF(OR(AY22="BOA_033E",AY22="BOA_011G"),"OCOGS - Spares - Transfer Price Overhead","OFSS - ORCL Consulting Prod Cost I/C"),"")</f>
-        <v/>
+      <c r="BL22" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AY23" s="4" t="s">
+      <c r="AY23" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="BF23" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="BG23" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="BL23" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="BN23" s="0" t="str">
-        <f aca="false">IF(AND(BL23="LAG",OR(BG23="OCOGS - Spares - Transfer Price Overhead",BG23="OFSS - ORCL Consulting Prod Cost I/C")),IF(OR(AY23="BOA_033E",AY23="BOA_011G"),"OCOGS - Spares - Transfer Price Overhead","OFSS - ORCL Consulting Prod Cost I/C"),"")</f>
-        <v>OCOGS - Spares - Transfer Price Overhead</v>
+      <c r="BF23" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="BG23" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="BL23" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="BN23" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AY24" s="4" t="s">
+      <c r="AY24" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="BF24" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="BG24" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="BL24" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="BN24" s="0" t="str">
-        <f aca="false">IF(AND(BL24="LAG",OR(BG24="OCOGS - Spares - Transfer Price Overhead",BG24="OFSS - ORCL Consulting Prod Cost I/C")),IF(OR(AY24="BOA_033E",AY24="BOA_011G"),"OCOGS - Spares - Transfer Price Overhead","OFSS - ORCL Consulting Prod Cost I/C"),"")</f>
-        <v>OCOGS - Spares - Transfer Price Overhead</v>
+      <c r="BF24" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="BG24" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="BL24" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="BN24" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AY25" s="4" t="s">
+      <c r="AY25" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="BF25" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="BG25" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="BL25" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="BN25" s="0" t="str">
-        <f aca="false">IF(AND(BL25="LAG",OR(BG25="OCOGS - Spares - Transfer Price Overhead",BG25="OFSS - ORCL Consulting Prod Cost I/C")),IF(OR(AY25="BOA_033E",AY25="BOA_011G"),"OCOGS - Spares - Transfer Price Overhead","OFSS - ORCL Consulting Prod Cost I/C"),"")</f>
-        <v>OCOGS - Spares - Transfer Price Overhead</v>
+      <c r="BF25" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="BG25" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="BL25" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="BN25" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AY26" s="10" t="s">
+      <c r="AY26" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="BG26" s="8" t="s">
+      <c r="BG26" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="BL26" s="0" t="s">
+      <c r="BL26" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="BN26" s="0" t="str">
-        <f aca="false">IF(AND(BL26="LAG",OR(BG26="OCOGS - Spares - Transfer Price Overhead",BG26="OFSS - ORCL Consulting Prod Cost I/C")),IF(OR(AY26="BOA_033E",AY26="BOA_011G"),"OCOGS - Spares - Transfer Price Overhead","OFSS - ORCL Consulting Prod Cost I/C"),"")</f>
-        <v/>
-      </c>
     </row>
     <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AY27" s="10" t="s">
+      <c r="AY27" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="BG27" s="8" t="s">
+      <c r="BG27" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="BL27" s="0" t="s">
+      <c r="BL27" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="BN27" s="0" t="str">
-        <f aca="false">IF(AND(BL27="LAG",OR(BG27="OCOGS - Spares - Transfer Price Overhead",BG27="OFSS - ORCL Consulting Prod Cost I/C")),IF(OR(AY27="BOA_033E",AY27="BOA_011G"),"OCOGS - Spares - Transfer Price Overhead","OFSS - ORCL Consulting Prod Cost I/C"),"")</f>
-        <v/>
-      </c>
     </row>
     <row r="28" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AY28" s="10" t="s">
+      <c r="AY28" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="BG28" s="8" t="s">
+      <c r="BG28" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="BL28" s="0" t="s">
+      <c r="BL28" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="BN28" s="0" t="str">
-        <f aca="false">IF(AND(BL28="LAG",OR(BG28="OCOGS - Spares - Transfer Price Overhead",BG28="OFSS - ORCL Consulting Prod Cost I/C")),IF(OR(AY28="BOA_033E",AY28="BOA_011G"),"OCOGS - Spares - Transfer Price Overhead","OFSS - ORCL Consulting Prod Cost I/C"),"")</f>
-        <v/>
-      </c>
     </row>
     <row r="29" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AY29" s="10" t="s">
+      <c r="AY29" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="BG29" s="8" t="s">
+      <c r="BG29" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="BL29" s="0" t="s">
+      <c r="BL29" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="BN29" s="0" t="str">
-        <f aca="false">IF(AND(BL29="LAG",OR(BG29="OCOGS - Spares - Transfer Price Overhead",BG29="OFSS - ORCL Consulting Prod Cost I/C")),IF(OR(AY29="BOA_033E",AY29="BOA_011G"),"OCOGS - Spares - Transfer Price Overhead","OFSS - ORCL Consulting Prod Cost I/C"),"")</f>
-        <v/>
-      </c>
     </row>
     <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AY30" s="10" t="s">
+      <c r="AY30" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="BG30" s="8" t="s">
+      <c r="BG30" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="BL30" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="BN30" s="0" t="str">
-        <f aca="false">IF(AND(BL30="LAG",OR(BG30="OCOGS - Spares - Transfer Price Overhead",BG30="OFSS - ORCL Consulting Prod Cost I/C")),IF(OR(AY30="BOA_033E",AY30="BOA_011G"),"OCOGS - Spares - Transfer Price Overhead","OFSS - ORCL Consulting Prod Cost I/C"),"")</f>
-        <v/>
+      <c r="BL30" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AY31" s="10" t="s">
+      <c r="AY31" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="BG31" s="8" t="s">
+      <c r="BG31" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="BL31" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="BN31" s="0" t="str">
-        <f aca="false">IF(AND(BL31="LAG",OR(BG31="OCOGS - Spares - Transfer Price Overhead",BG31="OFSS - ORCL Consulting Prod Cost I/C")),IF(OR(AY31="BOA_033E",AY31="BOA_011G"),"OCOGS - Spares - Transfer Price Overhead","OFSS - ORCL Consulting Prod Cost I/C"),"")</f>
-        <v/>
+      <c r="BL31" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AY32" s="0" t="s">
+      <c r="AY32" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="BG32" s="8" t="s">
+      <c r="BG32" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="BL32" s="0" t="s">
+      <c r="BL32" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="BN32" s="0" t="str">
-        <f aca="false">IF(AND(BL32="LAG",OR(BG32="OCOGS - Spares - Transfer Price Overhead",BG32="OFSS - ORCL Consulting Prod Cost I/C")),IF(OR(AY32="BOA_033E",AY32="BOA_011G"),"OCOGS - Spares - Transfer Price Overhead","OFSS - ORCL Consulting Prod Cost I/C"),"")</f>
-        <v/>
-      </c>
     </row>
     <row r="33" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AY33" s="0" t="s">
+      <c r="AY33" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="BG33" s="8" t="s">
+      <c r="BG33" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="BL33" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="BN33" s="0" t="str">
-        <f aca="false">IF(AND(BL33="LAG",OR(BG33="OCOGS - Spares - Transfer Price Overhead",BG33="OFSS - ORCL Consulting Prod Cost I/C")),IF(OR(AY33="BOA_033E",AY33="BOA_011G"),"OCOGS - Spares - Transfer Price Overhead","OFSS - ORCL Consulting Prod Cost I/C"),"")</f>
-        <v/>
+      <c r="BL33" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AY34" s="0" t="s">
+      <c r="AY34" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="BG34" s="8" t="s">
+      <c r="BG34" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="BL34" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="BN34" s="0" t="str">
-        <f aca="false">IF(AND(BL34="LAG",OR(BG34="OCOGS - Spares - Transfer Price Overhead",BG34="OFSS - ORCL Consulting Prod Cost I/C")),IF(OR(AY34="BOA_033E",AY34="BOA_011G"),"OCOGS - Spares - Transfer Price Overhead","OFSS - ORCL Consulting Prod Cost I/C"),"")</f>
-        <v/>
+      <c r="BL34" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AY35" s="0" t="s">
+      <c r="AY35" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="BG35" s="8" t="s">
+      <c r="BG35" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="BL35" s="0" t="s">
+      <c r="BL35" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="BN35" s="0" t="str">
-        <f aca="false">IF(AND(BL35="LAG",OR(BG35="OCOGS - Spares - Transfer Price Overhead",BG35="OFSS - ORCL Consulting Prod Cost I/C")),IF(OR(AY35="BOA_033E",AY35="BOA_011G"),"OCOGS - Spares - Transfer Price Overhead","OFSS - ORCL Consulting Prod Cost I/C"),"")</f>
-        <v/>
-      </c>
     </row>
     <row r="36" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AY36" s="0" t="s">
+      <c r="AY36" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="BG36" s="8" t="s">
+      <c r="BG36" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="BL36" s="0" t="s">
+      <c r="BL36" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="BN36" s="0" t="str">
-        <f aca="false">IF(AND(BL36="LAG",OR(BG36="OCOGS - Spares - Transfer Price Overhead",BG36="OFSS - ORCL Consulting Prod Cost I/C")),IF(OR(AY36="BOA_033E",AY36="BOA_011G"),"OCOGS - Spares - Transfer Price Overhead","OFSS - ORCL Consulting Prod Cost I/C"),"")</f>
-        <v/>
-      </c>
     </row>
     <row r="37" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AY37" s="0" t="s">
+      <c r="AY37" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="BG37" s="8" t="s">
+      <c r="BG37" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="BL37" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="BN37" s="0" t="str">
-        <f aca="false">IF(AND(BL37="LAG",OR(BG37="OCOGS - Spares - Transfer Price Overhead",BG37="OFSS - ORCL Consulting Prod Cost I/C")),IF(OR(AY37="BOA_033E",AY37="BOA_011G"),"OCOGS - Spares - Transfer Price Overhead","OFSS - ORCL Consulting Prod Cost I/C"),"")</f>
-        <v/>
+      <c r="BL37" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AY38" s="0" t="s">
+      <c r="AY38" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="BG38" s="8" t="s">
+      <c r="BG38" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="BL38" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="BN38" s="0" t="str">
-        <f aca="false">IF(AND(BL38="LAG",OR(BG38="OCOGS - Spares - Transfer Price Overhead",BG38="OFSS - ORCL Consulting Prod Cost I/C")),IF(OR(AY38="BOA_033E",AY38="BOA_011G"),"OCOGS - Spares - Transfer Price Overhead","OFSS - ORCL Consulting Prod Cost I/C"),"")</f>
-        <v/>
+      <c r="BL38" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AY39" s="0" t="s">
+      <c r="AY39" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="BG39" s="8" t="s">
+      <c r="BG39" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="BL39" s="0" t="s">
+      <c r="BL39" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="BN39" s="0" t="str">
-        <f aca="false">IF(AND(BL39="LAG",OR(BG39="OCOGS - Spares - Transfer Price Overhead",BG39="OFSS - ORCL Consulting Prod Cost I/C")),IF(OR(AY39="BOA_033E",AY39="BOA_011G"),"OCOGS - Spares - Transfer Price Overhead","OFSS - ORCL Consulting Prod Cost I/C"),"")</f>
-        <v/>
-      </c>
     </row>
     <row r="40" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AY40" s="0" t="s">
+      <c r="AY40" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="BG40" s="8" t="s">
+      <c r="BG40" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="BL40" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="BN40" s="0" t="str">
-        <f aca="false">IF(AND(BL40="LAG",OR(BG40="OCOGS - Spares - Transfer Price Overhead",BG40="OFSS - ORCL Consulting Prod Cost I/C")),IF(OR(AY40="BOA_033E",AY40="BOA_011G"),"OCOGS - Spares - Transfer Price Overhead","OFSS - ORCL Consulting Prod Cost I/C"),"")</f>
-        <v/>
+      <c r="BL40" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AY41" s="0" t="s">
+      <c r="AY41" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="BG41" s="8" t="s">
+      <c r="BG41" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="BL41" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="BN41" s="0" t="str">
-        <f aca="false">IF(AND(BL41="LAG",OR(BG41="OCOGS - Spares - Transfer Price Overhead",BG41="OFSS - ORCL Consulting Prod Cost I/C")),IF(OR(AY41="BOA_033E",AY41="BOA_011G"),"OCOGS - Spares - Transfer Price Overhead","OFSS - ORCL Consulting Prod Cost I/C"),"")</f>
-        <v/>
+      <c r="BL41" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AY42" s="0" t="s">
+      <c r="AY42" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="BG42" s="8" t="s">
+      <c r="BG42" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="BL42" s="0" t="s">
+      <c r="BL42" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="BN42" s="0" t="str">
-        <f aca="false">IF(AND(BL42="LAG",OR(BG42="OCOGS - Spares - Transfer Price Overhead",BG42="OFSS - ORCL Consulting Prod Cost I/C")),IF(OR(AY42="BOA_033E",AY42="BOA_011G"),"OCOGS - Spares - Transfer Price Overhead","OFSS - ORCL Consulting Prod Cost I/C"),"")</f>
-        <v/>
-      </c>
     </row>
     <row r="43" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AY43" s="0" t="s">
+      <c r="AY43" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="BG43" s="8" t="s">
+      <c r="BG43" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="BL43" s="0" t="s">
+      <c r="BL43" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="BN43" s="0" t="str">
-        <f aca="false">IF(AND(BL43="LAG",OR(BG43="OCOGS - Spares - Transfer Price Overhead",BG43="OFSS - ORCL Consulting Prod Cost I/C")),IF(OR(AY43="BOA_033E",AY43="BOA_011G"),"OCOGS - Spares - Transfer Price Overhead","OFSS - ORCL Consulting Prod Cost I/C"),"")</f>
-        <v/>
-      </c>
     </row>
     <row r="44" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AY44" s="0" t="s">
+      <c r="AY44" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="BG44" s="8" t="s">
+      <c r="BG44" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="BL44" s="0" t="s">
+      <c r="BL44" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="BN44" s="0" t="str">
-        <f aca="false">IF(AND(BL44="LAG",OR(BG44="OCOGS - Spares - Transfer Price Overhead",BG44="OFSS - ORCL Consulting Prod Cost I/C")),IF(OR(AY44="BOA_033E",AY44="BOA_011G"),"OCOGS - Spares - Transfer Price Overhead","OFSS - ORCL Consulting Prod Cost I/C"),"")</f>
-        <v/>
-      </c>
     </row>
     <row r="45" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AY45" s="10" t="s">
+      <c r="AY45" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="BG45" s="8" t="s">
+      <c r="BG45" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="BL45" s="0" t="s">
+      <c r="BL45" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="BN45" s="0" t="str">
-        <f aca="false">IF(AND(BL45="LAG",OR(BG45="OCOGS - Spares - Transfer Price Overhead",BG45="OFSS - ORCL Consulting Prod Cost I/C")),IF(OR(AY45="BOA_033E",AY45="BOA_011G"),"OCOGS - Spares - Transfer Price Overhead","OFSS - ORCL Consulting Prod Cost I/C"),"")</f>
-        <v/>
       </c>
     </row>
   </sheetData>
